--- a/data/trans_camb/IP1011-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP1011-Edad-trans_camb.xlsx
@@ -787,27 +787,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 1,29</t>
+          <t>-0,48; 1,05</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 0,0</t>
+          <t>-1,44; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 0,5</t>
+          <t>-1,27; 0,5</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 0,59</t>
+          <t>-1,21; 0,61</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 0,6</t>
+          <t>-0,74; 0,45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,67</t>
+          <t>0,0; 1,94</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,03</t>
+          <t>0,0; 1,05</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 1,17</t>
+          <t>-0,68; 1,16</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 0,0</t>
+          <t>-1,88; 0,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 0,0</t>
+          <t>-1,83; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 0,0</t>
+          <t>-1,86; 0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 0,4</t>
+          <t>-0,83; 0,4</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 0,0</t>
+          <t>-1,34; 0,0</t>
         </is>
       </c>
     </row>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 0,41</t>
+          <t>-0,34; 0,42</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 0,0</t>
+          <t>-0,7; 0,0</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 0,11</t>
+          <t>-0,62; 0,1</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 0,23</t>
+          <t>-0,31; 0,23</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-85,29; 330,07</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">

--- a/data/trans_camb/IP1011-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP1011-Edad-trans_camb.xlsx
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 1,05</t>
+          <t>-0,48; 1,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 0,0</t>
+          <t>-1,37; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 0,5</t>
+          <t>-1,29; 0,5</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 0,61</t>
+          <t>-1,23; 0,58</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 0,45</t>
+          <t>-0,65; 0,46</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 0,3</t>
+          <t>-0,79; 0,25</t>
         </is>
       </c>
     </row>
@@ -953,7 +953,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,94</t>
+          <t>0,0; 2,06</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,05</t>
+          <t>0,0; 1,19</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 1,16</t>
+          <t>-0,68; 1,17</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 0,0</t>
+          <t>-2,26; 0,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 0,0</t>
+          <t>-1,62; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 0,0</t>
+          <t>-1,63; 0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 0,4</t>
+          <t>-0,8; 0,4</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 0,0</t>
+          <t>-1,19; 0,0</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 0,42</t>
+          <t>-0,35; 0,41</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 0,0</t>
+          <t>-0,66; 0,0</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 0,27</t>
+          <t>-0,55; 0,27</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 0,1</t>
+          <t>-0,58; 0,11</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 0,23</t>
+          <t>-0,32; 0,23</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 0,01</t>
+          <t>-0,43; 0,01</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 331,0</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">

--- a/data/trans_camb/IP1011-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP1011-Edad-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -749,17 +749,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-0,26</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-0,24</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0,08</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-0,24</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,26</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 1,27</t>
+          <t>-1,34; 0,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 0,0</t>
+          <t>-1,07; 0,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 0,5</t>
+          <t>-0,48; 1,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 0,58</t>
+          <t>-1,18; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 0,46</t>
+          <t>-0,62; 0,6</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 0,25</t>
+          <t>-0,79; 0,3</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-51,02%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-46,18%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>34,89%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-51,02%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-46,18%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -905,17 +905,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,41</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,41</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 1,67</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,06</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,19</t>
+          <t>0,0; 1,03</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -981,17 +981,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-0,32</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-0,32</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>0,04</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>-0,34</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-0,32</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,32</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 1,17</t>
+          <t>-2,12; 0,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 0,0</t>
+          <t>-1,94; 0,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 0,0</t>
+          <t>-0,69; 1,17</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 0,0</t>
+          <t>-1,7; 0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 0,4</t>
+          <t>-0,81; 0,4</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 0,0</t>
+          <t>-1,12; 0,0</t>
         </is>
       </c>
     </row>
@@ -1137,17 +1137,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>12,45%</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-0,1</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-0,18</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>0,01</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>-0,19</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-0,1</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-0,18</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 0,41</t>
+          <t>-0,54; 0,27</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 0,0</t>
+          <t>-0,62; 0,11</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 0,27</t>
+          <t>-0,36; 0,41</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 0,11</t>
+          <t>-0,65; 0,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 0,23</t>
+          <t>-0,33; 0,23</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 0,01</t>
+          <t>-0,46; 0,01</t>
         </is>
       </c>
     </row>
@@ -1293,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-35,13%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-64,88%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>7,44%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-35,13%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-64,88%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 331,0</t>
+          <t>-85,29; 330,07</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
